--- a/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplate.xlsx
@@ -60,7 +60,7 @@
     <t>{.disabledName}</t>
   </si>
   <si>
-    <t>{.createByName}</t>
+    <t>{.createUserName}</t>
   </si>
   <si>
     <t>{.createTime}</t>
@@ -679,9 +679,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1000,14 +1006,14 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="18.25" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="24.5" customWidth="1"/>
-    <col min="5" max="5" width="49.25" customWidth="1"/>
-    <col min="6" max="6" width="13.5" customWidth="1"/>
-    <col min="7" max="7" width="14.375" customWidth="1"/>
-    <col min="8" max="8" width="19.375" customWidth="1"/>
+    <col min="1" max="1" width="18.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="49.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="19.375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:8">
@@ -1037,28 +1043,28 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
